--- a/exports/CDSL_full_report.xlsx
+++ b/exports/CDSL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>794.75</v>
+        <v>754.5</v>
       </c>
       <c r="I2" t="n">
         <v>774.8072157970648</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>-2.39</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>2.9</v>
       </c>
       <c r="M2" t="n">
         <v>0.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
         <v>-0.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>683.5</v>
+        <v>722.5</v>
       </c>
       <c r="I3" t="n">
         <v>705.4907604626276</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K3" t="n">
-        <v>9.41</v>
+        <v>4.24</v>
       </c>
       <c r="L3" t="n">
         <v>5.69</v>
@@ -612,7 +647,7 @@
         <v>4.38</v>
       </c>
       <c r="N3" t="n">
-        <v>5.76</v>
+        <v>8.43</v>
       </c>
       <c r="O3" t="n">
         <v>-5.5</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.31</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>725.5</v>
+        <v>718.9</v>
       </c>
       <c r="I4" t="n">
         <v>725.4731998953848</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>0.42</v>
+        <v>-0.5</v>
       </c>
       <c r="L4" t="n">
         <v>3.6</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>564</v>
+        <v>593.1</v>
       </c>
       <c r="I5" t="n">
         <v>566.1305539277881</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>21.55</v>
+        <v>17.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.4</v>
@@ -726,7 +785,7 @@
         <v>2.41</v>
       </c>
       <c r="N5" t="n">
-        <v>5.05</v>
+        <v>10.55</v>
       </c>
       <c r="O5" t="n">
         <v>-1.48</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>10.62</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>563.5</v>
+        <v>556</v>
       </c>
       <c r="I6" t="n">
         <v>558.2579016860561</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.99</v>
+        <v>-6.26</v>
       </c>
       <c r="L6" t="n">
-        <v>5.99</v>
+        <v>6.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85</v>
+        <v>1.42</v>
       </c>
       <c r="N6" t="n">
         <v>4.41</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.41</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>565.5</v>
+        <v>580.55</v>
       </c>
       <c r="I7" t="n">
         <v>571.6137457241744</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.71</v>
+        <v>-4.42</v>
       </c>
       <c r="L7" t="n">
-        <v>4.72</v>
+        <v>5.63</v>
       </c>
       <c r="M7" t="n">
         <v>1.77</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.97</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>588.5</v>
+        <v>580.9</v>
       </c>
       <c r="I8" t="n">
         <v>581.4041660277342</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>1.37</v>
+        <v>0.06</v>
       </c>
       <c r="L8" t="n">
         <v>5.26</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.39</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>599.5</v>
+        <v>626.5</v>
       </c>
       <c r="I9" t="n">
         <v>618.0339351626645</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.2</v>
+        <v>-7.85</v>
       </c>
       <c r="L9" t="n">
-        <v>4.56</v>
+        <v>10.43</v>
       </c>
       <c r="M9" t="n">
         <v>0.59</v>
       </c>
       <c r="N9" t="n">
-        <v>3.14</v>
+        <v>4.17</v>
       </c>
       <c r="O9" t="n">
         <v>3.14</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>667</v>
+        <v>655.5</v>
       </c>
       <c r="I10" t="n">
         <v>657.3091375615658</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>6.46</v>
+        <v>4.63</v>
       </c>
       <c r="L10" t="n">
         <v>4.66</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.97</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44879.38541666666</v>
+        <v>44879.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>608.75</v>
+        <v>627.5</v>
       </c>
       <c r="I11" t="n">
         <v>623.935305925317</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>7.13</v>
+        <v>4.27</v>
       </c>
       <c r="L11" t="n">
         <v>4.18</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44904.55208333334</v>
+        <v>44907.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>605</v>
+        <v>602.35</v>
       </c>
       <c r="I12" t="n">
         <v>604.9803878129421</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.59</v>
+        <v>-4.01</v>
       </c>
       <c r="L12" t="n">
-        <v>3.75</v>
+        <v>4.29</v>
       </c>
       <c r="M12" t="n">
         <v>0.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>570.25</v>
+        <v>581</v>
       </c>
       <c r="I13" t="n">
         <v>573.9637191614704</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>5.33</v>
+        <v>3.54</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>551.5</v>
+        <v>549.2</v>
       </c>
       <c r="I14" t="n">
         <v>550.8039359466147</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.08</v>
+        <v>-5.47</v>
       </c>
       <c r="L14" t="n">
-        <v>5.34</v>
+        <v>5.68</v>
       </c>
       <c r="M14" t="n">
         <v>0.03</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>499.7</v>
+        <v>512.25</v>
       </c>
       <c r="I15" t="n">
         <v>504.5696694830839</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>9.01</v>
+        <v>6.73</v>
       </c>
       <c r="L15" t="n">
         <v>0.89</v>
@@ -1296,7 +1475,7 @@
         <v>3.66</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>-0.63</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>489.85</v>
+        <v>487.1</v>
       </c>
       <c r="I16" t="n">
         <v>487.9492440464948</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.37</v>
+        <v>-4.91</v>
       </c>
       <c r="L16" t="n">
-        <v>4.83</v>
+        <v>5.22</v>
       </c>
       <c r="M16" t="n">
         <v>1.71</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.2</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>466</v>
+        <v>471.5</v>
       </c>
       <c r="I17" t="n">
         <v>468.0516345471793</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
         <v>2.11</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.06</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>525</v>
+        <v>514.6</v>
       </c>
       <c r="I18" t="n">
         <v>517.408666486273</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K18" t="n">
-        <v>11.35</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
@@ -1467,7 +1682,7 @@
         <v>2.29</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>2.2</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45103.55208333334</v>
+        <v>45104.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>523.25</v>
+        <v>536.95</v>
       </c>
       <c r="I19" t="n">
         <v>529.4632695208746</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.68</v>
+        <v>-4.34</v>
       </c>
       <c r="L19" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.97</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>597.5</v>
+        <v>590</v>
       </c>
       <c r="I20" t="n">
         <v>595.2881091036559</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K20" t="n">
-        <v>11.28</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>2.41</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.03</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45173.55208333334</v>
+        <v>45174.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>577.1</v>
+        <v>600.7</v>
       </c>
       <c r="I21" t="n">
         <v>586.3313795269345</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>2.19</v>
+        <v>-1.81</v>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>3.73</v>
       </c>
       <c r="M21" t="n">
         <v>0.76</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>6.13</v>
       </c>
       <c r="O21" t="n">
         <v>-1.1</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.19</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>667.9</v>
+        <v>649.5</v>
       </c>
       <c r="I22" t="n">
         <v>654.5658191890752</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>11.19</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>3.82</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.99</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="I23" t="n">
         <v>699.1521690221369</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.08</v>
+        <v>-12.09</v>
       </c>
       <c r="L23" t="n">
-        <v>9.699999999999999</v>
+        <v>12.32</v>
       </c>
       <c r="M23" t="n">
         <v>6.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3.69</v>
+        <v>5.59</v>
       </c>
       <c r="O23" t="n">
         <v>-3.85</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.62</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>957.6</v>
+        <v>904.5</v>
       </c>
       <c r="I24" t="n">
         <v>915.1205412559648</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>31.54</v>
+        <v>24.24</v>
       </c>
       <c r="L24" t="n">
         <v>5.56</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>902.5</v>
+        <v>934</v>
       </c>
       <c r="I25" t="n">
         <v>921.4069258499072</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>0.22</v>
+        <v>-3.26</v>
       </c>
       <c r="L25" t="n">
         <v>5.98</v>
       </c>
       <c r="M25" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>3.71</v>
       </c>
       <c r="O25" t="n">
         <v>-5.39</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.04</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45342.55208333334</v>
+        <v>45343.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>921.25</v>
+        <v>913.3</v>
       </c>
       <c r="I26" t="n">
         <v>916.6736101709857</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.37</v>
+        <v>-2.22</v>
       </c>
       <c r="L26" t="n">
         <v>3.24</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>7.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45348.55208333334</v>
+        <v>45349.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>950</v>
+        <v>964.4</v>
       </c>
       <c r="I27" t="n">
         <v>962.6831890673996</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.02</v>
+        <v>-5.6</v>
       </c>
       <c r="L27" t="n">
-        <v>6.13</v>
+        <v>7.3</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N27" t="n">
         <v>2.18</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45362.38541666666</v>
+        <v>45362.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>915.45</v>
+        <v>903.5</v>
       </c>
       <c r="I28" t="n">
         <v>906.6093238019527</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.08</v>
+        <v>-6.31</v>
       </c>
       <c r="L28" t="n">
-        <v>6.15</v>
+        <v>6.37</v>
       </c>
       <c r="M28" t="n">
         <v>0.13</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.66</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45372.38541666666</v>
+        <v>45372.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>875.9</v>
+        <v>885</v>
       </c>
       <c r="I29" t="n">
         <v>884.4586029305817</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="L29" t="n">
         <v>1.66</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.74</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45421.55208333334</v>
+        <v>45422.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1040</v>
+        <v>994.4</v>
       </c>
       <c r="I30" t="n">
         <v>999.3691038322559</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>17.51</v>
+        <v>12.36</v>
       </c>
       <c r="L30" t="n">
         <v>5.37</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.28</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1075.5</v>
+        <v>1084.2</v>
       </c>
       <c r="I31" t="n">
         <v>1079.032481684628</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.16</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>8.66</v>
+        <v>10.91</v>
       </c>
       <c r="M31" t="n">
         <v>0.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1080</v>
+        <v>1004.5</v>
       </c>
       <c r="I32" t="n">
         <v>1024.028798455411</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.39</v>
+        <v>-7.35</v>
       </c>
       <c r="L32" t="n">
-        <v>6.01</v>
+        <v>15.37</v>
       </c>
       <c r="M32" t="n">
         <v>0.74</v>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>8.56</v>
       </c>
       <c r="O32" t="n">
         <v>0.5600000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45470.55208333334</v>
+        <v>45471.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1005</v>
+        <v>1164.5</v>
       </c>
       <c r="I33" t="n">
         <v>1044.183058962885</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05</v>
+        <v>-15.93</v>
       </c>
       <c r="L33" t="n">
-        <v>7.31</v>
+        <v>16.11</v>
       </c>
       <c r="M33" t="n">
-        <v>1.43</v>
+        <v>7.46</v>
       </c>
       <c r="N33" t="n">
-        <v>3.66</v>
+        <v>19.77</v>
       </c>
       <c r="O33" t="n">
         <v>-8.56</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.68</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1171.5</v>
+        <v>1156.25</v>
       </c>
       <c r="I34" t="n">
         <v>1168.425257882282</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>-0.71</v>
       </c>
       <c r="L34" t="n">
         <v>8.970000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.73</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1223</v>
+        <v>1262.95</v>
       </c>
       <c r="I35" t="n">
         <v>1244.802327117495</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.77</v>
+        <v>-9.23</v>
       </c>
       <c r="L35" t="n">
-        <v>7.89</v>
+        <v>12.21</v>
       </c>
       <c r="M35" t="n">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="N35" t="n">
-        <v>3.64</v>
+        <v>4.98</v>
       </c>
       <c r="O35" t="n">
         <v>-5.73</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.9</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1435.3</v>
+        <v>1418.1</v>
       </c>
       <c r="I36" t="n">
         <v>1425.404967802736</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>13.65</v>
+        <v>12.28</v>
       </c>
       <c r="L36" t="n">
         <v>2.29</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.78</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1381.75</v>
+        <v>1444.95</v>
       </c>
       <c r="I37" t="n">
         <v>1432.39439520077</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>2.56</v>
+        <v>-1.89</v>
       </c>
       <c r="L37" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
         <v>0.87</v>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>4.34</v>
       </c>
       <c r="O37" t="n">
         <v>-1.21</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1441</v>
+        <v>1414.45</v>
       </c>
       <c r="I38" t="n">
         <v>1428.355893288176</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.27</v>
+        <v>-2.11</v>
       </c>
       <c r="L38" t="n">
         <v>5.04</v>
       </c>
       <c r="M38" t="n">
-        <v>0.67</v>
+        <v>1.66</v>
       </c>
       <c r="N38" t="n">
         <v>2.29</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>7.59</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1376</v>
+        <v>1469</v>
       </c>
       <c r="I39" t="n">
         <v>1463.064511202875</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>2.72</v>
+        <v>-3.86</v>
       </c>
       <c r="L39" t="n">
-        <v>2.94</v>
+        <v>4.48</v>
       </c>
       <c r="M39" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="N39" t="n">
-        <v>0.25</v>
+        <v>7.01</v>
       </c>
       <c r="O39" t="n">
         <v>-1.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.95</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1470.85</v>
+        <v>1414.85</v>
       </c>
       <c r="I40" t="n">
         <v>1463.541378557441</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>0.13</v>
+        <v>-3.69</v>
       </c>
       <c r="L40" t="n">
         <v>6.06</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1542</v>
+        <v>1574.9</v>
       </c>
       <c r="I41" t="n">
         <v>1556.658915560522</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.99</v>
+        <v>-11.31</v>
       </c>
       <c r="L41" t="n">
-        <v>10.97</v>
+        <v>13.79</v>
       </c>
       <c r="M41" t="n">
         <v>2.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1524.95</v>
+        <v>1465</v>
       </c>
       <c r="I42" t="n">
         <v>1501.95262561006</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.17</v>
+        <v>-6.98</v>
       </c>
       <c r="L42" t="n">
-        <v>3.74</v>
+        <v>7.33</v>
       </c>
       <c r="M42" t="n">
         <v>0.45</v>
       </c>
       <c r="N42" t="n">
-        <v>2.68</v>
+        <v>5.18</v>
       </c>
       <c r="O42" t="n">
         <v>2.08</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45622.38541666666</v>
+        <v>45622.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1568.2</v>
+        <v>1588</v>
       </c>
       <c r="I43" t="n">
         <v>1569.227098681348</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.04</v>
+        <v>-8.4</v>
       </c>
       <c r="L43" t="n">
-        <v>8.390000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="M43" t="n">
         <v>1.63</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.78</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1877.7</v>
+        <v>1864</v>
       </c>
       <c r="I44" t="n">
         <v>1865.479571720401</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>18.24</v>
+        <v>17.38</v>
       </c>
       <c r="L44" t="n">
         <v>1.35</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.11</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1123.7</v>
+        <v>1159</v>
       </c>
       <c r="I45" t="n">
         <v>1138.368197879279</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>88</v>
+        <v>88.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>39.72</v>
+        <v>37.82</v>
       </c>
       <c r="L45" t="n">
         <v>1.72</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.6</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1204.5</v>
+        <v>1125</v>
       </c>
       <c r="I46" t="n">
         <v>1156.012620997755</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>3.93</v>
+        <v>-2.93</v>
       </c>
       <c r="L46" t="n">
-        <v>2.58</v>
+        <v>6.82</v>
       </c>
       <c r="M46" t="n">
-        <v>0.09</v>
+        <v>10.34</v>
       </c>
       <c r="N46" t="n">
-        <v>2.86</v>
+        <v>3.69</v>
       </c>
       <c r="O46" t="n">
         <v>4.32</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>9.31</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1219.9</v>
+        <v>1230.9</v>
       </c>
       <c r="I47" t="n">
         <v>1229.762489945166</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.44</v>
+        <v>-9.41</v>
       </c>
       <c r="L47" t="n">
-        <v>8.58</v>
+        <v>9.42</v>
       </c>
       <c r="M47" t="n">
         <v>3.75</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1277.5</v>
+        <v>1252</v>
       </c>
       <c r="I48" t="n">
         <v>1276.938339427107</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
-        <v>3.79</v>
+        <v>1.71</v>
       </c>
       <c r="L48" t="n">
         <v>1.34</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.02</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45790.38541666666</v>
+        <v>45790.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1316.2</v>
+        <v>1323</v>
       </c>
       <c r="I49" t="n">
         <v>1316.97447925526</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.13</v>
+        <v>-5.67</v>
       </c>
       <c r="L49" t="n">
-        <v>5.79</v>
+        <v>5.83</v>
       </c>
       <c r="M49" t="n">
         <v>4.39</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1738</v>
+        <v>1666.5</v>
       </c>
       <c r="I50" t="n">
         <v>1697.118726754926</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>31.37</v>
+        <v>25.96</v>
       </c>
       <c r="L50" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="N50" t="n">
-        <v>2.83</v>
+        <v>5.38</v>
       </c>
       <c r="O50" t="n">
         <v>3.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>9.15</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1724</v>
+        <v>1749.4</v>
       </c>
       <c r="I51" t="n">
         <v>1749.093710021353</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.45</v>
+        <v>-4.97</v>
       </c>
       <c r="L51" t="n">
-        <v>4.41</v>
+        <v>5.86</v>
       </c>
       <c r="M51" t="n">
-        <v>0.32</v>
+        <v>1.8</v>
       </c>
       <c r="N51" t="n">
         <v>2.93</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.37</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1747.2</v>
+        <v>1704.7</v>
       </c>
       <c r="I52" t="n">
         <v>1706.091443237605</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.13</v>
+        <v>-2.56</v>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>3.09</v>
       </c>
       <c r="M52" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="N52" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>1.44</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.62</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1536.7</v>
+        <v>1572</v>
       </c>
       <c r="I53" t="n">
         <v>1564.188116807482</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>9.859999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="L53" t="n">
         <v>2.89</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.31</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1540.6</v>
+        <v>1506.7</v>
       </c>
       <c r="I54" t="n">
         <v>1516.147548637764</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>-2</v>
+        <v>-4.15</v>
       </c>
       <c r="L54" t="n">
-        <v>3.63</v>
+        <v>4.26</v>
       </c>
       <c r="M54" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="O54" t="n">
         <v>6.01</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.75</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1479</v>
+        <v>1516.5</v>
       </c>
       <c r="I55" t="n">
         <v>1498.209235755192</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>1.84</v>
+        <v>-0.65</v>
       </c>
       <c r="L55" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="M55" t="n">
         <v>0.21</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.84</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1547.4</v>
+        <v>1527.5</v>
       </c>
       <c r="I56" t="n">
         <v>1533.03161925677</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>2.04</v>
+        <v>0.73</v>
       </c>
       <c r="L56" t="n">
         <v>3.51</v>
       </c>
       <c r="M56" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="N56" t="n">
-        <v>1.8</v>
+        <v>2.42</v>
       </c>
       <c r="O56" t="n">
         <v>2.03</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1503.9</v>
+        <v>1528</v>
       </c>
       <c r="I57" t="n">
         <v>1518.14296274428</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>1.55</v>
+        <v>-0.03</v>
       </c>
       <c r="L57" t="n">
         <v>1.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.04</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1592</v>
+        <v>1551.2</v>
       </c>
       <c r="I58" t="n">
         <v>1569.200165941327</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>4.19</v>
+        <v>1.52</v>
       </c>
       <c r="L58" t="n">
         <v>1.63</v>
@@ -3747,7 +4442,7 @@
         <v>0.43</v>
       </c>
       <c r="N58" t="n">
-        <v>1.49</v>
+        <v>3.46</v>
       </c>
       <c r="O58" t="n">
         <v>2.55</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.09</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1600.9</v>
+        <v>1649.3</v>
       </c>
       <c r="I59" t="n">
         <v>1602.987202452464</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.2</v>
+        <v>-6.32</v>
       </c>
       <c r="L59" t="n">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="M59" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>3.11</v>
+        <v>3.26</v>
       </c>
       <c r="O59" t="n">
         <v>-3.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.29</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1591</v>
+        <v>1564.4</v>
       </c>
       <c r="I60" t="n">
         <v>1570.444235145574</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.53</v>
+        <v>-5.15</v>
       </c>
       <c r="L60" t="n">
-        <v>4.79</v>
+        <v>5.65</v>
       </c>
       <c r="M60" t="n">
         <v>0.43</v>
       </c>
       <c r="N60" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="O60" t="n">
         <v>3.26</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.04</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1241</v>
+        <v>1342.8</v>
       </c>
       <c r="I61" t="n">
         <v>1325.069161638473</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K61" t="n">
-        <v>20.67</v>
+        <v>14.17</v>
       </c>
       <c r="L61" t="n">
         <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>0.98</v>
+        <v>7.3</v>
       </c>
       <c r="N61" t="n">
-        <v>2.88</v>
+        <v>8.15</v>
       </c>
       <c r="O61" t="n">
         <v>-2.28</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.37</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46078.55208333334</v>
+        <v>46079.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1326</v>
+        <v>1286.1</v>
       </c>
       <c r="I62" t="n">
         <v>1311.296058810789</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.25</v>
+        <v>-4.22</v>
       </c>
       <c r="L62" t="n">
         <v>4.47</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.5</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1187.5</v>
+        <v>1225.8</v>
       </c>
       <c r="I63" t="n">
         <v>1216.549012316806</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K63" t="n">
-        <v>7.67</v>
+        <v>4.69</v>
       </c>
       <c r="L63" t="n">
         <v>2.95</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.9</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46111.38541666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1143.2</v>
+        <v>1121</v>
       </c>
       <c r="I64" t="n">
         <v>1133.444308018944</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.74</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>7.2</v>
+        <v>8.93</v>
       </c>
       <c r="M64" t="n">
         <v>1.5</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.49</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1202</v>
+        <v>1282.8</v>
       </c>
       <c r="I65" t="n">
         <v>1216.172419508771</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.23</v>
+        <v>-14.43</v>
       </c>
       <c r="L65" t="n">
-        <v>7.93</v>
+        <v>15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>5.52</v>
       </c>
       <c r="N65" t="n">
-        <v>5.64</v>
+        <v>7.4</v>
       </c>
       <c r="O65" t="n">
         <v>-4.15</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.02</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1323.5</v>
+        <v>1311.3</v>
       </c>
       <c r="I66" t="n">
         <v>1313.088889219601</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K66" t="n">
-        <v>3.17</v>
+        <v>2.22</v>
       </c>
       <c r="L66" t="n">
         <v>2.59</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.04</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46168.38541666666</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="I67" t="n">
         <v>1230.073944366903</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K67" t="n">
-        <v>6.73</v>
+        <v>6.05</v>
       </c>
       <c r="L67" t="n">
         <v>2.61</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.71</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>1206.5</v>
+        <v>1190</v>
       </c>
       <c r="I68" t="n">
         <v>1206.35801719419</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.07</v>
+        <v>-3.41</v>
       </c>
       <c r="L68" t="n">
-        <v>3.07</v>
+        <v>3.81</v>
       </c>
       <c r="M68" t="n">
         <v>1.38</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.43</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1228</v>
+        <v>1266.8</v>
       </c>
       <c r="I69" t="n">
         <v>1243.262182928054</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.19</v>
+        <v>-6.45</v>
       </c>
       <c r="L69" t="n">
-        <v>3.39</v>
+        <v>6.55</v>
       </c>
       <c r="M69" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="N69" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="O69" t="n">
         <v>-2.2</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.93</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46202.38541666666</v>
+        <v>46202.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>1304.1</v>
+        <v>1301.8</v>
       </c>
       <c r="I70" t="n">
         <v>1302.366594126857</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="L70" t="n">
         <v>1.56</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>5.26</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1348</v>
+        <v>1421</v>
       </c>
       <c r="I71" t="n">
         <v>1369.712813674681</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.55</v>
+        <v>-9.16</v>
       </c>
       <c r="L71" t="n">
-        <v>4.92</v>
+        <v>10.02</v>
       </c>
       <c r="M71" t="n">
         <v>0.51</v>
       </c>
       <c r="N71" t="n">
-        <v>2.67</v>
+        <v>6.19</v>
       </c>
       <c r="O71" t="n">
         <v>-1.15</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>8.08</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1363.4</v>
+        <v>1334.3</v>
       </c>
       <c r="I72" t="n">
         <v>1361.962826566609</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.05</v>
+        <v>-6.1</v>
       </c>
       <c r="L72" t="n">
-        <v>4.81</v>
+        <v>6.33</v>
       </c>
       <c r="M72" t="n">
         <v>0.6899999999999999</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>6.64</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1345.9</v>
+        <v>1386.6</v>
       </c>
       <c r="I73" t="n">
         <v>1375.119838521972</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.87</v>
+        <v>-3.92</v>
       </c>
       <c r="L73" t="n">
-        <v>2.29</v>
+        <v>5.06</v>
       </c>
       <c r="M73" t="n">
         <v>0.82</v>
       </c>
       <c r="N73" t="n">
-        <v>1.41</v>
+        <v>3.14</v>
       </c>
       <c r="O73" t="n">
         <v>-1.64</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.24</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1391</v>
+        <v>1368.9</v>
       </c>
       <c r="I74" t="n">
         <v>1369.762192161445</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K74" t="n">
-        <v>0.32</v>
+        <v>-1.28</v>
       </c>
       <c r="L74" t="n">
         <v>2.94</v>
       </c>
       <c r="M74" t="n">
-        <v>0.13</v>
+        <v>0.93</v>
       </c>
       <c r="N74" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O74" t="n">
         <v>3.14</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>4.82</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1349.5</v>
+        <v>1374.6</v>
       </c>
       <c r="I75" t="n">
         <v>1365.071324763207</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K75" t="n">
-        <v>1.42</v>
+        <v>-0.42</v>
       </c>
       <c r="L75" t="n">
         <v>5.05</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>6.48</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1316.3</v>
+        <v>1296</v>
       </c>
       <c r="I76" t="n">
         <v>1304.07246382286</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.24</v>
+        <v>-5.72</v>
       </c>
       <c r="L76" t="n">
-        <v>4.48</v>
+        <v>5.86</v>
       </c>
       <c r="M76" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O76" t="n">
         <v>2.63</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>5.64</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>1285.8</v>
+        <v>1303.3</v>
       </c>
       <c r="I77" t="n">
         <v>1298.44629258449</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K77" t="n">
-        <v>0.79</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L77" t="n">
         <v>1.7</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>5.22</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>1270.7</v>
+        <v>1233.3</v>
       </c>
       <c r="I78" t="n">
         <v>1240.602865897535</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.5</v>
+        <v>-5.37</v>
       </c>
       <c r="L78" t="n">
-        <v>2.86</v>
+        <v>5.47</v>
       </c>
       <c r="M78" t="n">
         <v>0.06</v>
       </c>
       <c r="N78" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="O78" t="n">
         <v>0.35</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,12 @@
       <c r="Q79" t="n">
         <v>10</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="11">
@@ -7139,7 +8092,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.59</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8102,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.17</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8112,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8122,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.72</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8132,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8142,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.11</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8152,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.75</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8162,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.97</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8172,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8182,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8192,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
@@ -7249,7 +8202,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.55</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="26">
@@ -7259,7 +8212,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8222,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.67</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8232,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
